--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,27 +1021,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134633126</v>
+        <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>106358</v>
+        <v>110333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221157</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåbär</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vaccinium myrtillus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1049,24 +1049,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvattala N om , Srm</t>
+          <t>Kvattala, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606476</v>
+        <v>606804</v>
       </c>
       <c r="R5" t="n">
-        <v>6557871</v>
+        <v>6557752</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,12 +1094,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,35 +1112,34 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633126</t>
+          <t>https://artportalen.se/Sighting/136932671</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97563529</v>
+        <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>102419</v>
+        <v>110333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,37 +1147,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älmhult, Srm</t>
+          <t>Kvattala, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606449</v>
+        <v>606806</v>
       </c>
       <c r="R6" t="n">
-        <v>6557865</v>
+        <v>6557738</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,17 +1209,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,23 +1223,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Lennart Sundh</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1243,38 +1245,38 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97563529</t>
+          <t>https://artportalen.se/Sighting/136932674</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134633252</v>
+        <v>136932675</v>
       </c>
       <c r="B7" t="n">
-        <v>102496</v>
+        <v>106406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221317</v>
+        <v>221141</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,17 +1286,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvattala N om , Srm</t>
+          <t>Kvattala, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606476</v>
+        <v>606770</v>
       </c>
       <c r="R7" t="n">
-        <v>6557871</v>
+        <v>6557740</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,12 +1320,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,52 +1338,51 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Torr gräsmark</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633252</t>
+          <t>https://artportalen.se/Sighting/136932675</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97529552</v>
+        <v>134633126</v>
       </c>
       <c r="B8" t="n">
-        <v>102560</v>
+        <v>106358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222133</v>
+        <v>221157</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1390,19 +1391,23 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvattala, N om vid vägen, Srm</t>
+          <t>Kvattala N om , Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606401</v>
+        <v>606476</v>
       </c>
       <c r="R8" t="n">
-        <v>6557861</v>
+        <v>6557871</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,12 +1431,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,38 +1445,39 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>torrbacke på gravfält</t>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97529552</t>
+          <t>https://artportalen.se/Sighting/134633126</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97529312</v>
+        <v>97563529</v>
       </c>
       <c r="B9" t="n">
-        <v>99754</v>
+        <v>102419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,37 +1485,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222295</v>
+        <v>221317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvattala, N om vid vägen, Srm</t>
+          <t>Älmhult, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606401</v>
+        <v>606449</v>
       </c>
       <c r="R9" t="n">
-        <v>6557861</v>
+        <v>6557865</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,12 +1539,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,55 +1563,59 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>torrbacke på gravfält</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Emma Karlsson, Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97529312</t>
+          <t>https://artportalen.se/Sighting/97563529</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134633109</v>
+        <v>134633252</v>
       </c>
       <c r="B10" t="n">
-        <v>100806</v>
+        <v>102496</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222584</v>
+        <v>221317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1681,33 +1696,33 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633109</t>
+          <t>https://artportalen.se/Sighting/134633252</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134633097</v>
+        <v>97529552</v>
       </c>
       <c r="B11" t="n">
-        <v>101324</v>
+        <v>102560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222782</v>
+        <v>222133</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1716,23 +1731,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvattala N om , Srm</t>
+          <t>Kvattala, N om vid vägen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606476</v>
+        <v>606401</v>
       </c>
       <c r="R11" t="n">
-        <v>6557871</v>
+        <v>6557861</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,12 +1767,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>1978-05-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>1978-05-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,81 +1781,76 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>torrbacke på gravfält</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633097</t>
+          <t>https://artportalen.se/Sighting/97529552</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134633093</v>
+        <v>97529312</v>
       </c>
       <c r="B12" t="n">
-        <v>99472</v>
+        <v>99754</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222812</v>
+        <v>222295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvattala N om , Srm</t>
+          <t>Kvattala, N om vid vägen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>606476</v>
+        <v>606401</v>
       </c>
       <c r="R12" t="n">
-        <v>6557871</v>
+        <v>6557861</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,12 +1874,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>1978-05-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>1978-05-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,81 +1888,84 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>torrbacke på gravfält</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633093</t>
+          <t>https://artportalen.se/Sighting/97529312</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134651362</v>
+        <v>136932670</v>
       </c>
       <c r="B13" t="n">
-        <v>102871</v>
+        <v>99990</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223037</v>
+        <v>222295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvattala N om , Srm</t>
+          <t>Kvattala, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>606476</v>
+        <v>606809</v>
       </c>
       <c r="R13" t="n">
-        <v>6557871</v>
+        <v>6557746</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1980,12 +1989,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,35 +2007,34 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gräsmark</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134651362</t>
+          <t>https://artportalen.se/Sighting/136932670</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134633106</v>
+        <v>134633109</v>
       </c>
       <c r="B14" t="n">
-        <v>107697</v>
+        <v>100806</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,19 +2042,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224273</v>
+        <v>222584</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig ängskovall</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Melampyrum pratense var. pratense</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -2125,36 +2137,40 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633106</t>
+          <t>https://artportalen.se/Sighting/134633109</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134651249</v>
+        <v>134633097</v>
       </c>
       <c r="B15" t="n">
-        <v>101823</v>
+        <v>101324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224932</v>
+        <v>222782</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig backsmörblomma</t>
+          <t>Vitsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -2214,6 +2230,11 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
@@ -2228,16 +2249,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134651249</t>
+          <t>https://artportalen.se/Sighting/134633097</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134633276</v>
+        <v>134633093</v>
       </c>
       <c r="B16" t="n">
-        <v>103908</v>
+        <v>99472</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,19 +2266,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>225103</v>
+        <v>222812</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig sälg</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Salix caprea subsp. caprea</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -2336,36 +2361,40 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633276</t>
+          <t>https://artportalen.se/Sighting/134633093</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134631843</v>
+        <v>134651362</v>
       </c>
       <c r="B17" t="n">
-        <v>102640</v>
+        <v>102871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>265350</v>
+        <v>223037</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanligt jungfrulin</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygala vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -2427,7 +2456,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Vägslänt</t>
+          <t>Gräsmark</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2443,6 +2472,766 @@
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651362</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136932669</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kvattala, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>606869</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6557760</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932669</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136932672</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kvattala, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>606800</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6557746</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932672</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136932673</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kvattala, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>606798</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6557749</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932673</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134633106</v>
+      </c>
+      <c r="B21" t="n">
+        <v>107697</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>224273</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vanlig ängskovall</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense var. pratense</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Torr gräsmark</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134633106</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134651249</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101823</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>224932</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vanlig backsmörblomma</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651249</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134633276</v>
+      </c>
+      <c r="B23" t="n">
+        <v>103908</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>225103</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vanlig sälg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134633276</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134631843</v>
+      </c>
+      <c r="B24" t="n">
+        <v>102640</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134631843</t>
         </is>
@@ -2466,6 +3255,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,27 +1251,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136932675</v>
+        <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>106406</v>
+        <v>110333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1279,21 +1279,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvattala, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606770</v>
+        <v>606752</v>
       </c>
       <c r="R7" t="n">
-        <v>6557740</v>
+        <v>6557762</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1346,7 +1345,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Saga Samuelsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1356,16 +1355,16 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136932675</t>
+          <t>https://artportalen.se/Sighting/136949569</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134633126</v>
+        <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106358</v>
+        <v>106406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,16 +1372,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221157</v>
+        <v>221141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåbär</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Vaccinium myrtillus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1397,17 +1396,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvattala N om , Srm</t>
+          <t>Kvattala, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606476</v>
+        <v>606770</v>
       </c>
       <c r="R8" t="n">
-        <v>6557871</v>
+        <v>6557740</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,12 +1430,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,73 +1448,76 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633126</t>
+          <t>https://artportalen.se/Sighting/136932675</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97563529</v>
+        <v>134633126</v>
       </c>
       <c r="B9" t="n">
-        <v>102419</v>
+        <v>106358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221317</v>
+        <v>221157</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Älmhult, Srm</t>
+          <t>Kvattala N om , Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>606449</v>
+        <v>606476</v>
       </c>
       <c r="R9" t="n">
-        <v>6557865</v>
+        <v>6557871</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,17 +1541,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,42 +1555,39 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Lennart Sundh</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97563529</t>
+          <t>https://artportalen.se/Sighting/134633126</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134633252</v>
+        <v>97563529</v>
       </c>
       <c r="B10" t="n">
-        <v>102496</v>
+        <v>102419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,23 +1613,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvattala N om , Srm</t>
+          <t>Älmhult, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>606476</v>
+        <v>606449</v>
       </c>
       <c r="R10" t="n">
-        <v>6557871</v>
+        <v>6557865</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,12 +1649,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,39 +1668,42 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Torr gräsmark</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Emma Karlsson, Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633252</t>
+          <t>https://artportalen.se/Sighting/97563529</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97529552</v>
+        <v>134633252</v>
       </c>
       <c r="B11" t="n">
-        <v>102560</v>
+        <v>102496</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,37 +1711,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222133</v>
+        <v>221317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvattala, N om vid vägen, Srm</t>
+          <t>Kvattala N om , Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606401</v>
+        <v>606476</v>
       </c>
       <c r="R11" t="n">
-        <v>6557861</v>
+        <v>6557871</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,12 +1769,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,38 +1783,39 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>torrbacke på gravfält</t>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97529552</t>
+          <t>https://artportalen.se/Sighting/134633252</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97529312</v>
+        <v>97529552</v>
       </c>
       <c r="B12" t="n">
-        <v>99754</v>
+        <v>102560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,21 +1823,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222295</v>
+        <v>222133</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1910,16 +1913,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97529312</t>
+          <t>https://artportalen.se/Sighting/97529552</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136932670</v>
+        <v>97529312</v>
       </c>
       <c r="B13" t="n">
-        <v>99990</v>
+        <v>99754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,28 +1947,20 @@
           <t>Latourr.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvattala, Srm</t>
+          <t>Kvattala, N om vid vägen, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>606809</v>
+        <v>606401</v>
       </c>
       <c r="R13" t="n">
-        <v>6557746</v>
+        <v>6557861</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,12 +1984,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>1978-05-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>1978-05-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,80 +1998,84 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>torrbacke på gravfält</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Staffan Fridh</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136932670</t>
+          <t>https://artportalen.se/Sighting/97529312</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134633109</v>
+        <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100806</v>
+        <v>99990</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222584</v>
+        <v>222295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvattala N om , Srm</t>
+          <t>Kvattala, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>606476</v>
+        <v>606809</v>
       </c>
       <c r="R14" t="n">
-        <v>6557871</v>
+        <v>6557746</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,12 +2099,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,35 +2117,34 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Torr gräsmark</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633109</t>
+          <t>https://artportalen.se/Sighting/136932670</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134633097</v>
+        <v>134633109</v>
       </c>
       <c r="B15" t="n">
-        <v>101324</v>
+        <v>100806</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2154,16 +2152,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222782</v>
+        <v>222584</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2230,9 +2228,9 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2249,16 +2247,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633097</t>
+          <t>https://artportalen.se/Sighting/134633109</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134633093</v>
+        <v>134633097</v>
       </c>
       <c r="B16" t="n">
-        <v>99472</v>
+        <v>101324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,16 +2264,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222812</v>
+        <v>222782</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Vitsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Anemone nemorosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2361,16 +2359,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633093</t>
+          <t>https://artportalen.se/Sighting/134633097</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134651362</v>
+        <v>134633093</v>
       </c>
       <c r="B17" t="n">
-        <v>102871</v>
+        <v>99472</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,16 +2376,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>223037</v>
+        <v>222812</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2454,9 +2452,9 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gräsmark</t>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2473,16 +2471,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134651362</t>
+          <t>https://artportalen.se/Sighting/134633093</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136932669</v>
+        <v>134651362</v>
       </c>
       <c r="B18" t="n">
-        <v>99273</v>
+        <v>102871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,41 +2488,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223597</v>
+        <v>223037</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kvattala, Srm</t>
+          <t>Kvattala N om , Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>606869</v>
+        <v>606476</v>
       </c>
       <c r="R18" t="n">
-        <v>6557760</v>
+        <v>6557871</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2548,12 +2546,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,31 +2564,32 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gräsmark</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Staffan Fridh</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136932669</t>
+          <t>https://artportalen.se/Sighting/134651362</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136932672</v>
+        <v>136932669</v>
       </c>
       <c r="B19" t="n">
         <v>99273</v>
@@ -2616,7 +2615,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2629,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>606800</v>
+        <v>606869</v>
       </c>
       <c r="R19" t="n">
-        <v>6557746</v>
+        <v>6557760</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2695,13 +2694,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136932672</t>
+          <t>https://artportalen.se/Sighting/136932669</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136932673</v>
+        <v>136932672</v>
       </c>
       <c r="B20" t="n">
         <v>99273</v>
@@ -2727,7 +2726,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2740,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>606798</v>
+        <v>606800</v>
       </c>
       <c r="R20" t="n">
-        <v>6557749</v>
+        <v>6557746</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2806,16 +2805,16 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136932673</t>
+          <t>https://artportalen.se/Sighting/136932672</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134633106</v>
+        <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>107697</v>
+        <v>99273</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,37 +2822,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>224273</v>
+        <v>223597</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig ängskovall</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Melampyrum pratense var. pratense</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvattala N om , Srm</t>
+          <t>Kvattala, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>606476</v>
+        <v>606798</v>
       </c>
       <c r="R21" t="n">
-        <v>6557871</v>
+        <v>6557749</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2877,12 +2880,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,73 +2898,72 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Torr gräsmark</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633106</t>
+          <t>https://artportalen.se/Sighting/136932673</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134651249</v>
+        <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>101823</v>
+        <v>99273</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>224932</v>
+        <v>223597</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig backsmörblomma</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kvattala N om , Srm</t>
+          <t>Kvattala, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>606476</v>
+        <v>606827</v>
       </c>
       <c r="R22" t="n">
-        <v>6557871</v>
+        <v>6557747</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2985,12 +2987,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,34 +3001,37 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134651249</t>
+          <t>https://artportalen.se/Sighting/136949568</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134633276</v>
+        <v>134633106</v>
       </c>
       <c r="B23" t="n">
-        <v>103908</v>
+        <v>107697</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3034,16 +3039,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>225103</v>
+        <v>224273</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vanlig sälg</t>
+          <t>Vanlig ängskovall</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Salix caprea subsp. caprea</t>
+          <t>Melampyrum pratense var. pratense</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -3106,9 +3111,9 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3125,16 +3130,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134633276</t>
+          <t>https://artportalen.se/Sighting/134633106</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134631843</v>
+        <v>134651249</v>
       </c>
       <c r="B24" t="n">
-        <v>102640</v>
+        <v>101823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3142,16 +3147,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>265350</v>
+        <v>224932</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vanligt jungfrulin</t>
+          <t>Vanlig backsmörblomma</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygala vulgaris subsp. vulgaris</t>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -3214,11 +3219,6 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Vägslänt</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
@@ -3232,6 +3232,222 @@
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651249</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134633276</v>
+      </c>
+      <c r="B25" t="n">
+        <v>103908</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>225103</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vanlig sälg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134633276</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134631843</v>
+      </c>
+      <c r="B26" t="n">
+        <v>102640</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134631843</t>
         </is>
@@ -3262,6 +3478,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106406</v>
+        <v>106412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>99990</v>
+        <v>99996</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106412</v>
+        <v>106414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>99996</v>
+        <v>99998</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106414</v>
+        <v>106415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>99998</v>
+        <v>99999</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110342</v>
+        <v>110348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110342</v>
+        <v>110348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110342</v>
+        <v>110348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106415</v>
+        <v>106421</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>99999</v>
+        <v>100005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110348</v>
+        <v>110352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110348</v>
+        <v>110352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110348</v>
+        <v>110352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106421</v>
+        <v>106425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100005</v>
+        <v>100009</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110352</v>
+        <v>110354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110352</v>
+        <v>110354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110352</v>
+        <v>110354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106425</v>
+        <v>106427</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100009</v>
+        <v>100011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110354</v>
+        <v>110356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110354</v>
+        <v>110356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110354</v>
+        <v>110356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106427</v>
+        <v>106429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100011</v>
+        <v>100013</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110356</v>
+        <v>110369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110356</v>
+        <v>110369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110356</v>
+        <v>110369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106429</v>
+        <v>106442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100013</v>
+        <v>100026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110369</v>
+        <v>110371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110369</v>
+        <v>110371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110369</v>
+        <v>110371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106442</v>
+        <v>106444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100026</v>
+        <v>100028</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110371</v>
+        <v>110376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110371</v>
+        <v>110376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110371</v>
+        <v>110376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106444</v>
+        <v>106448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100028</v>
+        <v>100031</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110376</v>
+        <v>110398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110376</v>
+        <v>110398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110376</v>
+        <v>110398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106448</v>
+        <v>106467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100031</v>
+        <v>100041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110398</v>
+        <v>110399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110398</v>
+        <v>110399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110398</v>
+        <v>110399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100041</v>
+        <v>100042</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110399</v>
+        <v>110404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110399</v>
+        <v>110404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110399</v>
+        <v>110404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106468</v>
+        <v>106473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100042</v>
+        <v>100047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106473</v>
+        <v>106476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100047</v>
+        <v>100050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110407</v>
+        <v>110413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110407</v>
+        <v>110413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110407</v>
+        <v>110413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106476</v>
+        <v>106482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100050</v>
+        <v>100056</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110413</v>
+        <v>110414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110413</v>
+        <v>110414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110413</v>
+        <v>110414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110414</v>
+        <v>110426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110414</v>
+        <v>110426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110414</v>
+        <v>110426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106483</v>
+        <v>106495</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100056</v>
+        <v>100068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110426</v>
+        <v>110427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110426</v>
+        <v>110427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110426</v>
+        <v>110427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106495</v>
+        <v>106496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100068</v>
+        <v>100069</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110427</v>
+        <v>110430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110427</v>
+        <v>110430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110427</v>
+        <v>110430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106496</v>
+        <v>106499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100069</v>
+        <v>100072</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110430</v>
+        <v>110432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110430</v>
+        <v>110432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110430</v>
+        <v>110432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106499</v>
+        <v>106501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100072</v>
+        <v>100073</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136932671</v>
       </c>
       <c r="B5" t="n">
-        <v>110432</v>
+        <v>110436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136932674</v>
       </c>
       <c r="B6" t="n">
-        <v>110432</v>
+        <v>110436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136949569</v>
       </c>
       <c r="B7" t="n">
-        <v>110432</v>
+        <v>110436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136932675</v>
       </c>
       <c r="B8" t="n">
-        <v>106501</v>
+        <v>106505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136932670</v>
       </c>
       <c r="B14" t="n">
-        <v>100073</v>
+        <v>100076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136932669</v>
       </c>
       <c r="B19" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136932672</v>
       </c>
       <c r="B20" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>136932673</v>
       </c>
       <c r="B21" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136949568</v>
       </c>
       <c r="B22" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
